--- a/nodes_source_analyses/energy/transport/transport_car_using_electricity.converter.xlsx
+++ b/nodes_source_analyses/energy/transport/transport_car_using_electricity.converter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10621"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mathijsbijkerk/Projects/etdataset/nodes_source_analyses/energy/transport/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robin/Desktop/Quintel/etdataset/nodes_source_analyses/energy/transport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C10B89BA-2BDF-2F4A-B733-18BD27DA84F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5878226E-6CAE-994C-88C8-3ECF2DC8EFC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30080" yWindow="-18040" windowWidth="30080" windowHeight="16080" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31860" yWindow="500" windowWidth="28800" windowHeight="16160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover sheet" sheetId="14" r:id="rId1"/>
@@ -37,7 +37,7 @@
     <definedName name="Wp_to_kWp">#REF!</definedName>
     <definedName name="WP_to_MWp">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentManualCount="4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="136">
   <si>
     <t>Source</t>
   </si>
@@ -171,9 +171,6 @@
     <t>Author</t>
   </si>
   <si>
-    <t>Maria Tsagkaraki</t>
-  </si>
-  <si>
     <t>Legend</t>
   </si>
   <si>
@@ -246,55 +243,19 @@
     <t>km/MJ</t>
   </si>
   <si>
-    <t>cedelft-ecn-tno</t>
-  </si>
-  <si>
-    <t>p.64</t>
-  </si>
-  <si>
     <t>MJ/km</t>
   </si>
   <si>
-    <t>cedeltf-ecn-tno</t>
-  </si>
-  <si>
-    <t>Efficiency</t>
-  </si>
-  <si>
-    <t>http://refman.et-model.com/publications/1928</t>
-  </si>
-  <si>
     <t>http://www.fuelswitch.nl/files/files_news/natural_gas_in_transport_tno_ce_delft_ecn_4818.pdf</t>
   </si>
   <si>
     <t>cedelft-ecn-tno2</t>
   </si>
   <si>
-    <t>p.183</t>
-  </si>
-  <si>
     <t>http://refman.et-model.com/publications/2008</t>
   </si>
   <si>
     <t>http://www.energieakkoordser.nl/~/media/files/energieakkoord/nieuwsberichten/2014/brandstofvisie/verzamelde-kennisnotities-brandstoffmix.ashx</t>
-  </si>
-  <si>
-    <t>Used the latter efficiency as it is more recent and the source covers all technologies currently in the ETM</t>
-  </si>
-  <si>
-    <r>
-      <t>cedelft-ecn-tno</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2</t>
-    </r>
   </si>
   <si>
     <t>storage.volume</t>
@@ -506,18 +467,6 @@
     <t>http://statline.cbs.nl/Statweb/publication/?DM=SLNL&amp;PA=83497ned&amp;D1=0&amp;D2=a&amp;D3=0&amp;D4=5&amp;HDR=T,G3&amp;STB=G1,G2&amp;VW=T</t>
   </si>
   <si>
-    <t>vehicle km</t>
-  </si>
-  <si>
-    <t>mln vehicle km</t>
-  </si>
-  <si>
-    <t>passenger km</t>
-  </si>
-  <si>
-    <t>mld passenger km</t>
-  </si>
-  <si>
     <t>passenger km/vehicle km</t>
   </si>
   <si>
@@ -540,6 +489,33 @@
   </si>
   <si>
     <t>storage decay per hour</t>
+  </si>
+  <si>
+    <t>p.29</t>
+  </si>
+  <si>
+    <t>efficiency</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t> https://ce.nl/wp-content/uploads/2025/02/CE_Delft_210506_STREAM_Personenvervoer_2024_Def.pdf</t>
+  </si>
+  <si>
+    <t>p. 18</t>
+  </si>
+  <si>
+    <t>CE Delft (2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CE Delft </t>
+  </si>
+  <si>
+    <t>CE Delft</t>
+  </si>
+  <si>
+    <t>Robin de Smit</t>
   </si>
 </sst>
 </file>
@@ -563,6 +539,13 @@
       <color theme="1"/>
       <name val="Lettertype hoofdtekst"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -815,13 +798,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1125,634 +1101,634 @@
   </borders>
   <cellStyleXfs count="338">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="38" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="28" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="26" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="27" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="26" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="27" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="26" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="26" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="27" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="27" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="23" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="23" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="22" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="21" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="21" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="22" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="21" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="1" fontId="21" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="22" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="3"/>
     </xf>
-    <xf numFmtId="2" fontId="21" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="21" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="22" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="15" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="16" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="21" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="31" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="32" fillId="12" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="22" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="23" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="32" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="33" fillId="12" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="23" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="14" fontId="31" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="32" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="35" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="35" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="34" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="34" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="34" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="23" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="32" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="31" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="7" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="36" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="11" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="31" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="35" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="168" fontId="35" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="35" fillId="2" borderId="0" xfId="337" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="32" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="36" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="36" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="36" fillId="2" borderId="0" xfId="337" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="11" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="10" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="11" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="32" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="36" fillId="0" borderId="18" xfId="337" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="169" fontId="36" fillId="2" borderId="18" xfId="337" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="31" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="172" fontId="35" fillId="0" borderId="18" xfId="337" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="169" fontId="35" fillId="2" borderId="18" xfId="337" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="338">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -2111,94 +2087,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>139700</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000009000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5346700" y="1168400"/>
-          <a:ext cx="6502400" cy="1524000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>660400</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>279400</xdr:colOff>
-      <xdr:row>87</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="Picture 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5511800" y="6705600"/>
-          <a:ext cx="19431000" cy="9944100"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>1003300</xdr:colOff>
       <xdr:row>17</xdr:row>
@@ -2224,7 +2112,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2245,14 +2133,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>876300</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>1193800</xdr:colOff>
-      <xdr:row>111</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2268,7 +2156,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2289,13 +2177,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>115</xdr:row>
+      <xdr:row>61</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>158</xdr:row>
+      <xdr:row>104</xdr:row>
       <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2312,7 +2200,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2333,14 +2221,14 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>157</xdr:row>
+      <xdr:row>103</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>660400</xdr:colOff>
-      <xdr:row>200</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
+      <xdr:row>147</xdr:row>
+      <xdr:rowOff>16934</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2356,7 +2244,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2373,238 +2261,296 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>316173</xdr:colOff>
-      <xdr:row>199</xdr:row>
-      <xdr:rowOff>158467</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>36350</xdr:colOff>
-      <xdr:row>221</xdr:row>
-      <xdr:rowOff>4113</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>196515</xdr:rowOff>
     </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="8" name="Group 7">
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000008000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25F5551B-7720-6E04-1942-4E2DB88BC0DD}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="14336973" y="40646067"/>
-          <a:ext cx="13232977" cy="4366846"/>
-          <a:chOff x="9231573" y="32137067"/>
-          <a:chExt cx="12902777" cy="4417646"/>
+          <a:off x="8001000" y="1028700"/>
+          <a:ext cx="7772400" cy="2431715"/>
         </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="10" name="Picture 9">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000A000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="9231573" y="32137067"/>
-            <a:ext cx="12902777" cy="4417646"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="13" name="Rectangle 12">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000D000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="13195110" y="34022352"/>
-            <a:ext cx="1173708" cy="552735"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:solidFill>
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="3">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="2">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr lang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>254000</xdr:colOff>
-      <xdr:row>225</xdr:row>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>431800</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>622300</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>18831</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Rectangle 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{397FCAAC-D484-994E-B9A2-4CB5A3C95048}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8102600" y="2755900"/>
+          <a:ext cx="3721100" cy="323631"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>571500</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Rectangle 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45782DB2-646C-CF43-B2D2-093D0FBB9195}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8242300" y="4102100"/>
+          <a:ext cx="2984500" cy="520700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>245</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>88900</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="14" name="Group 13">
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="Picture 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000E000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{806B67A4-0ECE-194D-96F9-97DE40237697}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:srcRect b="28273"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="14274800" y="45872400"/>
-          <a:ext cx="17119601" cy="4152900"/>
-          <a:chOff x="9702800" y="37896800"/>
-          <a:chExt cx="16776701" cy="4152900"/>
+          <a:off x="15735300" y="1079500"/>
+          <a:ext cx="12890500" cy="5181600"/>
         </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="15" name="Picture 14">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000F000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="9702800" y="37896800"/>
-            <a:ext cx="16776701" cy="4152900"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="16" name="Rectangle 15">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000010000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="13367223" y="40003862"/>
-            <a:ext cx="1654792" cy="368490"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:solidFill>
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="3">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="2">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr lang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>177800</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Rectangle 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EF3C6FD6-F82B-F34B-92B9-3C867922EC5E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18300700" y="3797300"/>
+          <a:ext cx="2984500" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover Sheet"/>
       <sheetName val="Changelog"/>
@@ -3041,12 +2987,12 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="26" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="19" customWidth="1"/>
-    <col min="3" max="3" width="38.42578125" style="19" customWidth="1"/>
-    <col min="4" max="16384" width="10.85546875" style="19"/>
+    <col min="1" max="1" width="3.5" style="26" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="19" customWidth="1"/>
+    <col min="3" max="3" width="38.5" style="19" customWidth="1"/>
+    <col min="4" max="16384" width="10.83203125" style="19"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="24" customFormat="1">
@@ -3081,7 +3027,7 @@
         <v>35</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -3106,7 +3052,7 @@
     <row r="9" spans="1:3">
       <c r="A9" s="1"/>
       <c r="B9" s="74" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" s="75"/>
     </row>
@@ -3118,31 +3064,31 @@
     <row r="11" spans="1:3">
       <c r="A11" s="1"/>
       <c r="B11" s="76" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="78" t="s">
         <v>38</v>
-      </c>
-      <c r="C11" s="78" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" thickBot="1">
       <c r="A12" s="1"/>
       <c r="B12" s="76"/>
       <c r="C12" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="17" thickBot="1">
       <c r="A13" s="1"/>
       <c r="B13" s="76"/>
       <c r="C13" s="79" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1"/>
       <c r="B14" s="76"/>
       <c r="C14" s="77" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -3153,58 +3099,58 @@
     <row r="16" spans="1:3">
       <c r="A16" s="1"/>
       <c r="B16" s="76" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="80" t="s">
         <v>43</v>
-      </c>
-      <c r="C16" s="80" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="76"/>
       <c r="C17" s="81" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="76"/>
       <c r="C18" s="82" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1"/>
       <c r="B19" s="76"/>
       <c r="C19" s="83" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="84"/>
       <c r="C20" s="85" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1"/>
       <c r="B21" s="84"/>
       <c r="C21" s="86" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="84"/>
       <c r="C22" s="87" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="84"/>
       <c r="C23" s="88" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -3222,46 +3168,46 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="A2:J34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="4.140625" style="32" customWidth="1"/>
-    <col min="2" max="2" width="3.42578125" style="32" customWidth="1"/>
-    <col min="3" max="3" width="46.85546875" style="32" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="32" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" style="32" customWidth="1"/>
-    <col min="6" max="6" width="4.42578125" style="32" customWidth="1"/>
-    <col min="7" max="7" width="43.140625" style="32" customWidth="1"/>
-    <col min="8" max="8" width="5.140625" style="32" customWidth="1"/>
-    <col min="9" max="9" width="42.42578125" style="32" customWidth="1"/>
+    <col min="1" max="1" width="4.1640625" style="32" customWidth="1"/>
+    <col min="2" max="2" width="3.5" style="32" customWidth="1"/>
+    <col min="3" max="3" width="46.83203125" style="32" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="32" customWidth="1"/>
+    <col min="5" max="5" width="17.5" style="32" customWidth="1"/>
+    <col min="6" max="6" width="4.5" style="32" customWidth="1"/>
+    <col min="7" max="7" width="43.1640625" style="32" customWidth="1"/>
+    <col min="8" max="8" width="5.1640625" style="32" customWidth="1"/>
+    <col min="9" max="9" width="42.5" style="32" customWidth="1"/>
     <col min="10" max="10" width="5" style="32" customWidth="1"/>
-    <col min="11" max="16384" width="10.85546875" style="32"/>
+    <col min="11" max="16384" width="10.83203125" style="32"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10">
-      <c r="B2" s="172" t="s">
-        <v>119</v>
-      </c>
-      <c r="C2" s="173"/>
-      <c r="D2" s="173"/>
-      <c r="E2" s="174"/>
+      <c r="B2" s="176" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" s="177"/>
+      <c r="D2" s="177"/>
+      <c r="E2" s="178"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="175"/>
-      <c r="C3" s="176"/>
-      <c r="D3" s="176"/>
-      <c r="E3" s="177"/>
+      <c r="B3" s="179"/>
+      <c r="C3" s="180"/>
+      <c r="D3" s="180"/>
+      <c r="E3" s="181"/>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="175"/>
-      <c r="C4" s="176"/>
-      <c r="D4" s="176"/>
-      <c r="E4" s="177"/>
+      <c r="B4" s="179"/>
+      <c r="C4" s="180"/>
+      <c r="D4" s="180"/>
+      <c r="E4" s="181"/>
     </row>
     <row r="5" spans="2:10">
-      <c r="B5" s="178"/>
-      <c r="C5" s="179"/>
-      <c r="D5" s="179"/>
-      <c r="E5" s="180"/>
+      <c r="B5" s="182"/>
+      <c r="C5" s="183"/>
+      <c r="D5" s="183"/>
+      <c r="E5" s="184"/>
     </row>
     <row r="6" spans="2:10" ht="17" thickBot="1"/>
     <row r="7" spans="2:10">
@@ -3304,7 +3250,7 @@
     <row r="10" spans="2:10" s="13" customFormat="1" ht="17" thickBot="1">
       <c r="B10" s="21"/>
       <c r="C10" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D10" s="29"/>
       <c r="J10" s="14"/>
@@ -3312,32 +3258,30 @@
     <row r="11" spans="2:10" s="13" customFormat="1" ht="17" thickBot="1">
       <c r="B11" s="21"/>
       <c r="C11" s="62" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="E11" s="31">
         <f>'Research data'!H7</f>
-        <v>2.0422269584645436</v>
+        <v>1.6375</v>
       </c>
       <c r="F11" s="35"/>
-      <c r="G11" s="119" t="s">
-        <v>65</v>
-      </c>
+      <c r="G11" s="119"/>
       <c r="H11" s="28"/>
-      <c r="I11" s="124" t="s">
-        <v>73</v>
+      <c r="I11" s="188" t="s">
+        <v>134</v>
       </c>
       <c r="J11" s="14"/>
     </row>
     <row r="12" spans="2:10" s="13" customFormat="1" ht="17" thickBot="1">
       <c r="B12" s="21"/>
       <c r="C12" s="62" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="E12" s="126">
         <f>'Research data'!H8/1000</f>
@@ -3347,19 +3291,19 @@
       <c r="G12" s="119"/>
       <c r="H12" s="28"/>
       <c r="I12" s="158" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="J12" s="14"/>
     </row>
     <row r="13" spans="2:10" s="13" customFormat="1" ht="17" thickBot="1">
       <c r="B13" s="21"/>
       <c r="C13" s="62" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="E13" s="188">
+        <v>121</v>
+      </c>
+      <c r="E13" s="175">
         <f>'Research data'!H9</f>
         <v>5.4866766968530989E-5</v>
       </c>
@@ -3425,7 +3369,7 @@
       <c r="G16" s="35"/>
       <c r="H16" s="35"/>
       <c r="I16" s="133" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J16" s="94"/>
     </row>
@@ -3435,7 +3379,7 @@
         <v>31</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="E17" s="104">
         <v>3.7000000000000002E-3</v>
@@ -3458,7 +3402,7 @@
       <c r="A19" s="127"/>
       <c r="B19" s="128"/>
       <c r="C19" s="13" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="D19" s="97"/>
       <c r="E19" s="129"/>
@@ -3472,7 +3416,7 @@
       <c r="A20" s="127"/>
       <c r="B20" s="128"/>
       <c r="C20" s="131" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>22</v>
@@ -3486,7 +3430,7 @@
       </c>
       <c r="H20" s="131"/>
       <c r="I20" s="133" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J20" s="130"/>
     </row>
@@ -3494,7 +3438,7 @@
       <c r="A21" s="127"/>
       <c r="B21" s="128"/>
       <c r="C21" s="131" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>26</v>
@@ -3504,11 +3448,11 @@
       </c>
       <c r="F21" s="131"/>
       <c r="G21" s="131" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="H21" s="131"/>
       <c r="I21" s="133" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J21" s="130"/>
     </row>
@@ -3516,21 +3460,21 @@
       <c r="A22" s="127"/>
       <c r="B22" s="135"/>
       <c r="C22" s="136" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D22" s="137" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="E22" s="134">
         <v>0</v>
       </c>
       <c r="F22" s="136"/>
       <c r="G22" s="136" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H22" s="136"/>
       <c r="I22" s="133" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J22" s="138"/>
     </row>
@@ -3538,7 +3482,7 @@
       <c r="A23" s="127"/>
       <c r="B23" s="135"/>
       <c r="C23" s="136" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D23" s="137"/>
       <c r="E23" s="134">
@@ -3546,11 +3490,11 @@
       </c>
       <c r="F23" s="136"/>
       <c r="G23" s="136" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H23" s="136"/>
       <c r="I23" s="133" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J23" s="138"/>
     </row>
@@ -3558,7 +3502,7 @@
       <c r="A24" s="127"/>
       <c r="B24" s="135"/>
       <c r="C24" s="136" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D24" s="137"/>
       <c r="E24" s="134">
@@ -3566,11 +3510,11 @@
       </c>
       <c r="F24" s="136"/>
       <c r="G24" s="136" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="H24" s="136"/>
       <c r="I24" s="133" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J24" s="138"/>
     </row>
@@ -3578,7 +3522,7 @@
       <c r="A25" s="127"/>
       <c r="B25" s="135"/>
       <c r="C25" s="136" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="D25" s="137"/>
       <c r="E25" s="134">
@@ -3586,11 +3530,11 @@
       </c>
       <c r="F25" s="136"/>
       <c r="G25" s="136" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="H25" s="136"/>
       <c r="I25" s="133" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J25" s="138"/>
     </row>
@@ -3598,7 +3542,7 @@
       <c r="A26" s="127"/>
       <c r="B26" s="135"/>
       <c r="C26" s="136" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D26" s="137"/>
       <c r="E26" s="134">
@@ -3606,11 +3550,11 @@
       </c>
       <c r="F26" s="136"/>
       <c r="G26" s="131" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="H26" s="136"/>
       <c r="I26" s="133" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J26" s="138"/>
     </row>
@@ -3618,21 +3562,21 @@
       <c r="A27" s="127"/>
       <c r="B27" s="128"/>
       <c r="C27" s="131" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D27" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E27" s="184">
+      <c r="E27" s="171">
         <v>0.04</v>
       </c>
       <c r="F27" s="131"/>
-      <c r="G27" s="182" t="s">
-        <v>136</v>
+      <c r="G27" s="169" t="s">
+        <v>123</v>
       </c>
       <c r="H27" s="131"/>
-      <c r="I27" s="183" t="s">
-        <v>137</v>
+      <c r="I27" s="170" t="s">
+        <v>124</v>
       </c>
       <c r="J27" s="130"/>
     </row>
@@ -3640,10 +3584,10 @@
       <c r="A28" s="127"/>
       <c r="B28" s="128"/>
       <c r="C28" s="131" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="E28" s="134">
         <v>0</v>
@@ -3651,8 +3595,8 @@
       <c r="F28" s="131"/>
       <c r="G28" s="131"/>
       <c r="H28" s="131"/>
-      <c r="I28" s="181" t="s">
-        <v>135</v>
+      <c r="I28" s="168" t="s">
+        <v>122</v>
       </c>
       <c r="J28" s="130"/>
     </row>
@@ -3704,7 +3648,7 @@
       <c r="A32" s="127"/>
       <c r="B32" s="128"/>
       <c r="C32" s="131" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="D32" s="20" t="s">
         <v>1</v>
@@ -3714,11 +3658,11 @@
       </c>
       <c r="F32" s="131"/>
       <c r="G32" s="131" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="H32" s="131"/>
       <c r="I32" s="133" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="J32" s="130"/>
     </row>
@@ -3767,24 +3711,24 @@
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A2:Q15"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="3.42578125" style="42" customWidth="1"/>
-    <col min="3" max="3" width="35.85546875" style="42" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" style="42" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" style="42" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="9.42578125" style="42" customWidth="1"/>
-    <col min="7" max="7" width="3.140625" style="42" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" style="42" customWidth="1"/>
-    <col min="9" max="9" width="2.42578125" style="42" customWidth="1"/>
-    <col min="10" max="10" width="2.140625" style="42" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" style="42"/>
-    <col min="12" max="12" width="2.42578125" style="42" customWidth="1"/>
-    <col min="13" max="14" width="10.85546875" style="42"/>
-    <col min="15" max="15" width="13.85546875" style="42" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="1.7109375" style="42" customWidth="1"/>
+    <col min="1" max="2" width="3.5" style="42" customWidth="1"/>
+    <col min="3" max="3" width="35.83203125" style="42" customWidth="1"/>
+    <col min="4" max="4" width="16.5" style="42" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="13.83203125" style="42" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" style="42" customWidth="1"/>
+    <col min="7" max="7" width="3.1640625" style="42" customWidth="1"/>
+    <col min="8" max="8" width="9.5" style="42" customWidth="1"/>
+    <col min="9" max="9" width="2.5" style="42" customWidth="1"/>
+    <col min="10" max="10" width="2.1640625" style="42" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" style="42"/>
+    <col min="12" max="12" width="2.5" style="42" customWidth="1"/>
+    <col min="13" max="14" width="10.83203125" style="42"/>
+    <col min="15" max="15" width="13.83203125" style="42" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="1.6640625" style="42" customWidth="1"/>
     <col min="17" max="17" width="75" style="42" customWidth="1"/>
-    <col min="18" max="16384" width="10.85546875" style="42"/>
+    <col min="18" max="16384" width="10.83203125" style="42"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:17" ht="17" thickBot="1"/>
@@ -3802,7 +3746,7 @@
     <row r="4" spans="1:17" s="13" customFormat="1">
       <c r="B4" s="21"/>
       <c r="C4" s="89" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
@@ -3811,26 +3755,24 @@
       </c>
       <c r="G4" s="89"/>
       <c r="H4" s="89" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I4" s="89"/>
       <c r="J4" s="15"/>
-      <c r="K4" s="89" t="s">
-        <v>61</v>
-      </c>
+      <c r="K4" s="89"/>
       <c r="L4" s="89"/>
       <c r="M4" s="89" t="s">
-        <v>68</v>
+        <v>134</v>
       </c>
       <c r="N4" s="89" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="O4" s="89" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="P4" s="89"/>
       <c r="Q4" s="89" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="18" customHeight="1">
@@ -3846,7 +3788,7 @@
       <c r="A6" s="108"/>
       <c r="B6" s="109"/>
       <c r="C6" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="12"/>
@@ -3860,47 +3802,42 @@
       <c r="A7" s="108"/>
       <c r="B7" s="109"/>
       <c r="C7" s="110" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D7" s="110" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="E7" s="110"/>
       <c r="F7" s="111" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G7" s="112"/>
       <c r="H7" s="113">
         <f>M7</f>
-        <v>2.0422269584645436</v>
+        <v>1.6375</v>
       </c>
       <c r="I7" s="114"/>
-      <c r="K7" s="113">
-        <f>Notes!E212</f>
-        <v>1.8963536042885052</v>
-      </c>
+      <c r="K7" s="187"/>
       <c r="L7" s="115"/>
       <c r="M7" s="113">
-        <f>Notes!E210</f>
-        <v>2.0422269584645436</v>
+        <f>Notes!E14</f>
+        <v>1.6375</v>
       </c>
       <c r="N7" s="115"/>
       <c r="O7" s="115"/>
       <c r="P7" s="115"/>
-      <c r="Q7" s="123" t="s">
-        <v>72</v>
-      </c>
+      <c r="Q7" s="123"/>
     </row>
     <row r="8" spans="1:17" ht="17" thickBot="1">
       <c r="A8" s="108"/>
       <c r="B8" s="109"/>
       <c r="C8" s="110" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D8" s="110"/>
       <c r="E8" s="110"/>
       <c r="F8" s="125" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="G8" s="112"/>
       <c r="H8" s="155">
@@ -3913,27 +3850,27 @@
       <c r="M8" s="115"/>
       <c r="N8" s="115"/>
       <c r="O8" s="155">
-        <f>Notes!D120</f>
+        <f>Notes!D66</f>
         <v>100</v>
       </c>
       <c r="P8" s="115"/>
       <c r="Q8" s="154" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="17" thickBot="1">
       <c r="A9" s="108"/>
       <c r="B9" s="109"/>
       <c r="C9" s="110" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D9" s="110"/>
       <c r="E9" s="110"/>
-      <c r="F9" s="169" t="s">
-        <v>134</v>
+      <c r="F9" s="165" t="s">
+        <v>121</v>
       </c>
       <c r="G9" s="112"/>
-      <c r="H9" s="170">
+      <c r="H9" s="166">
         <f>N9</f>
         <v>5.4866766968530989E-5</v>
       </c>
@@ -3941,8 +3878,8 @@
       <c r="K9" s="115"/>
       <c r="L9" s="115"/>
       <c r="M9" s="115"/>
-      <c r="N9" s="171">
-        <f>Notes!E95</f>
+      <c r="N9" s="167">
+        <f>Notes!E41</f>
         <v>5.4866766968530989E-5</v>
       </c>
       <c r="O9" s="115"/>
@@ -3998,7 +3935,7 @@
     <row r="13" spans="1:17" ht="17" thickBot="1">
       <c r="B13" s="45"/>
       <c r="C13" s="12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="12"/>
@@ -4011,7 +3948,7 @@
     <row r="14" spans="1:17" ht="17" thickBot="1">
       <c r="B14" s="45"/>
       <c r="C14" s="93" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="12"/>
@@ -4034,7 +3971,7 @@
     <row r="15" spans="1:17" ht="17" thickBot="1">
       <c r="B15" s="45"/>
       <c r="C15" s="93" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" s="53"/>
       <c r="E15" s="53"/>
@@ -4066,18 +4003,18 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.1640625" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.42578125" style="63" customWidth="1"/>
-    <col min="2" max="2" width="4.140625" style="63" customWidth="1"/>
-    <col min="3" max="3" width="27.85546875" style="63" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" style="63" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" style="63" customWidth="1"/>
-    <col min="6" max="7" width="13.140625" style="63" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" style="68" customWidth="1"/>
-    <col min="9" max="9" width="31.85546875" style="68" customWidth="1"/>
-    <col min="10" max="10" width="98.42578125" style="63" customWidth="1"/>
-    <col min="11" max="16384" width="33.140625" style="63"/>
+    <col min="1" max="1" width="3.5" style="63" customWidth="1"/>
+    <col min="2" max="2" width="4.1640625" style="63" customWidth="1"/>
+    <col min="3" max="3" width="27.83203125" style="63" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" style="63" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" style="63" customWidth="1"/>
+    <col min="6" max="7" width="13.1640625" style="63" customWidth="1"/>
+    <col min="8" max="8" width="12.5" style="68" customWidth="1"/>
+    <col min="9" max="9" width="31.83203125" style="68" customWidth="1"/>
+    <col min="10" max="10" width="98.5" style="63" customWidth="1"/>
+    <col min="11" max="16384" width="33.1640625" style="63"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="17" thickBot="1"/>
@@ -4122,13 +4059,13 @@
         <v>19</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H5" s="17" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J5" s="15" t="s">
         <v>11</v>
@@ -4136,43 +4073,65 @@
     </row>
     <row r="6" spans="2:10">
       <c r="B6" s="66"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
-      <c r="J6" s="13"/>
+      <c r="C6" s="185" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="185" t="s">
+        <v>133</v>
+      </c>
+      <c r="E6" s="186" t="s">
+        <v>129</v>
+      </c>
+      <c r="F6" s="186">
+        <v>2024</v>
+      </c>
+      <c r="G6" s="186">
+        <v>2024</v>
+      </c>
+      <c r="H6" s="186">
+        <v>2026</v>
+      </c>
+      <c r="I6" s="186"/>
+      <c r="J6" s="186" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="7" spans="2:10">
       <c r="B7" s="66"/>
+      <c r="C7" s="117" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="186" t="s">
+        <v>133</v>
+      </c>
+      <c r="E7" s="186" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="186">
+        <v>2024</v>
+      </c>
+      <c r="G7" s="186">
+        <v>2024</v>
+      </c>
+      <c r="H7" s="186">
+        <v>2026</v>
+      </c>
+      <c r="I7" s="186"/>
+      <c r="J7" s="186" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="8" spans="2:10">
       <c r="B8" s="66"/>
-      <c r="C8" s="116" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="117" t="s">
+      <c r="C8" s="116"/>
+      <c r="D8" s="117"/>
+      <c r="E8" s="117"/>
+      <c r="F8" s="117"/>
+      <c r="G8" s="117"/>
+      <c r="H8" s="118"/>
+      <c r="I8" s="117"/>
+      <c r="J8" s="117" t="s">
         <v>61</v>
-      </c>
-      <c r="E8" s="117" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="117">
-        <v>2013</v>
-      </c>
-      <c r="G8" s="117">
-        <v>2012</v>
-      </c>
-      <c r="H8" s="118">
-        <v>42326</v>
-      </c>
-      <c r="I8" s="117" t="s">
-        <v>66</v>
-      </c>
-      <c r="J8" s="117" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="9" spans="2:10">
@@ -4187,7 +4146,7 @@
         <v>29</v>
       </c>
       <c r="D10" s="117" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="E10" s="120" t="s">
         <v>8</v>
@@ -4202,22 +4161,22 @@
         <v>42326</v>
       </c>
       <c r="I10" s="120" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="J10" s="117" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="2:10">
       <c r="B11" s="66"/>
       <c r="C11" s="62" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D11" s="141" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E11" s="141" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="F11" s="63">
         <v>2013</v>
@@ -4226,22 +4185,22 @@
         <v>2013</v>
       </c>
       <c r="H11" s="142" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="J11" s="141" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="2:10">
       <c r="B12" s="66"/>
       <c r="C12" s="156" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D12" s="141" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E12" s="141" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="F12" s="63">
         <v>2016</v>
@@ -4254,7 +4213,7 @@
       </c>
       <c r="I12" s="63"/>
       <c r="J12" s="63" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="2:10">
@@ -4267,10 +4226,10 @@
     </row>
     <row r="14" spans="2:10" s="159" customFormat="1">
       <c r="C14" s="159" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="D14" s="159" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E14" s="159" t="s">
         <v>8</v>
@@ -4279,11 +4238,11 @@
         <v>2015</v>
       </c>
       <c r="H14" s="160" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I14" s="160"/>
       <c r="J14" s="159" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="2:10" s="159" customFormat="1">
@@ -4292,10 +4251,10 @@
     </row>
     <row r="16" spans="2:10" s="159" customFormat="1">
       <c r="C16" s="159" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D16" s="159" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E16" s="159" t="s">
         <v>8</v>
@@ -4304,11 +4263,11 @@
         <v>2015</v>
       </c>
       <c r="H16" s="160" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="I16" s="160"/>
       <c r="J16" s="159" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -4369,19 +4328,19 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:M246"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
+  <dimension ref="A1:M196"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="3.42578125" style="145" customWidth="1"/>
+    <col min="1" max="2" width="3.5" style="145" customWidth="1"/>
     <col min="3" max="3" width="22" style="145" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.140625" style="145" customWidth="1"/>
+    <col min="4" max="4" width="24.1640625" style="145" customWidth="1"/>
     <col min="5" max="5" width="12" style="145" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" style="145" customWidth="1"/>
+    <col min="6" max="6" width="22.5" style="145" customWidth="1"/>
     <col min="7" max="7" width="13" style="145" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" style="145" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" style="145"/>
-    <col min="10" max="10" width="19.85546875" style="145" customWidth="1"/>
-    <col min="11" max="16384" width="10.85546875" style="145"/>
+    <col min="8" max="8" width="15.6640625" style="145" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" style="145"/>
+    <col min="10" max="10" width="19.83203125" style="145" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="145"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="17" thickBot="1"/>
@@ -4403,7 +4362,7 @@
       <c r="A3" s="148"/>
       <c r="B3" s="149"/>
       <c r="C3" s="150" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D3" s="150"/>
       <c r="E3" s="150" t="s">
@@ -4429,46 +4388,87 @@
     </row>
     <row r="7" spans="1:13">
       <c r="B7" s="152"/>
-      <c r="C7" s="145" t="s">
-        <v>64</v>
+      <c r="C7" s="185" t="s">
+        <v>132</v>
+      </c>
+      <c r="E7" s="145">
+        <v>0.8</v>
+      </c>
+      <c r="F7" s="145" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="B8" s="152"/>
+      <c r="C8" s="145" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" s="145">
+        <f>1/E7</f>
+        <v>1.25</v>
+      </c>
+      <c r="F8" s="145" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="9" spans="1:13">
       <c r="B9" s="152"/>
     </row>
     <row r="10" spans="1:13">
       <c r="B10" s="152"/>
-      <c r="C10" s="145" t="s">
-        <v>62</v>
-      </c>
-      <c r="E10" s="145">
-        <v>0.7</v>
-      </c>
-      <c r="F10" s="145" t="s">
-        <v>63</v>
-      </c>
+      <c r="C10" s="186" t="s">
+        <v>132</v>
+      </c>
+      <c r="D10" s="117"/>
+      <c r="E10" s="161">
+        <v>1.31</v>
+      </c>
+      <c r="F10" s="117" t="s">
+        <v>119</v>
+      </c>
+      <c r="G10" s="117"/>
     </row>
     <row r="11" spans="1:13">
       <c r="B11" s="152"/>
-      <c r="E11" s="145">
-        <f>1/E10</f>
-        <v>1.4285714285714286</v>
-      </c>
-      <c r="F11" s="145" t="s">
-        <v>60</v>
-      </c>
+      <c r="C11" s="117" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" s="117"/>
+      <c r="E11" s="117"/>
+      <c r="F11" s="117"/>
+      <c r="G11" s="117"/>
     </row>
     <row r="12" spans="1:13">
       <c r="B12" s="152"/>
+      <c r="C12" s="117"/>
+      <c r="D12" s="117"/>
+      <c r="E12" s="117"/>
+      <c r="F12" s="117"/>
+      <c r="G12" s="117"/>
     </row>
     <row r="13" spans="1:13">
       <c r="B13" s="152"/>
+      <c r="C13" s="117"/>
+      <c r="D13" s="117"/>
+      <c r="E13" s="117"/>
+      <c r="F13" s="117"/>
+      <c r="G13" s="117"/>
     </row>
     <row r="14" spans="1:13">
       <c r="B14" s="152"/>
+      <c r="C14" s="117"/>
+      <c r="D14" s="117" t="str">
+        <f>Dashboard!C11</f>
+        <v>output.passenger_kms</v>
+      </c>
+      <c r="E14" s="117">
+        <f>ROUND(E10*E8,6)</f>
+        <v>1.6375</v>
+      </c>
+      <c r="F14" s="117" t="s">
+        <v>120</v>
+      </c>
+      <c r="G14" s="187"/>
     </row>
     <row r="15" spans="1:13">
       <c r="B15" s="152"/>
@@ -4476,715 +4476,800 @@
     <row r="16" spans="1:13">
       <c r="B16" s="152"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:7">
       <c r="B17" s="152"/>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:7">
       <c r="B18" s="152"/>
-    </row>
-    <row r="19" spans="2:6">
+      <c r="C18" s="117"/>
+      <c r="D18" s="117"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="117"/>
+      <c r="G18" s="187"/>
+    </row>
+    <row r="19" spans="2:7">
       <c r="B19" s="152"/>
     </row>
-    <row r="20" spans="2:6">
+    <row r="20" spans="2:7">
       <c r="B20" s="152"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:7">
       <c r="B21" s="152"/>
       <c r="C21" s="145" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7">
       <c r="B22" s="152"/>
       <c r="E22" s="145">
         <v>13</v>
       </c>
       <c r="F22" s="145" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7">
       <c r="B23" s="152"/>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:7">
       <c r="B24" s="152"/>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:7">
       <c r="B25" s="152"/>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:7">
       <c r="B26" s="152"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:7">
       <c r="B27" s="152"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:7">
       <c r="B28" s="152"/>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:7">
       <c r="B29" s="152"/>
     </row>
-    <row r="30" spans="2:6">
+    <row r="30" spans="2:7">
       <c r="B30" s="152"/>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:7">
       <c r="B31" s="152"/>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:7">
       <c r="B32" s="152"/>
     </row>
-    <row r="33" spans="2:3">
+    <row r="33" spans="2:7">
       <c r="B33" s="152"/>
     </row>
-    <row r="34" spans="2:3">
+    <row r="34" spans="2:7">
       <c r="B34" s="152"/>
     </row>
-    <row r="35" spans="2:3" s="151" customFormat="1">
+    <row r="35" spans="2:7" s="151" customFormat="1">
       <c r="B35" s="153"/>
     </row>
-    <row r="36" spans="2:3">
+    <row r="36" spans="2:7">
       <c r="B36" s="152"/>
     </row>
-    <row r="37" spans="2:3">
+    <row r="37" spans="2:7">
       <c r="B37" s="152"/>
     </row>
-    <row r="38" spans="2:3">
+    <row r="38" spans="2:7">
       <c r="B38" s="152"/>
-    </row>
-    <row r="39" spans="2:3">
+      <c r="C38" s="145" t="s">
+        <v>96</v>
+      </c>
+      <c r="E38" s="145">
+        <v>85</v>
+      </c>
+      <c r="F38" s="145" t="s">
+        <v>67</v>
+      </c>
+      <c r="G38" s="145" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" ht="17" thickBot="1">
       <c r="B39" s="152"/>
       <c r="C39" s="145" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3">
+        <v>101</v>
+      </c>
+      <c r="E39" s="164">
+        <v>0.01</v>
+      </c>
+      <c r="G39" s="145" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" ht="17" thickBot="1">
       <c r="B40" s="152"/>
-    </row>
-    <row r="41" spans="2:3">
+      <c r="D40" s="172" t="s">
+        <v>125</v>
+      </c>
+      <c r="E40" s="173">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" ht="17" thickBot="1">
       <c r="B41" s="152"/>
-      <c r="C41" s="145" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3">
+      <c r="D41" s="172" t="s">
+        <v>126</v>
+      </c>
+      <c r="E41" s="174">
+        <f>1-(1-E40)^(1/(24*31))</f>
+        <v>5.4866766968530989E-5</v>
+      </c>
+    </row>
+    <row r="42" spans="2:7">
       <c r="B42" s="152"/>
-    </row>
-    <row r="43" spans="2:3">
+      <c r="E42" s="163"/>
+    </row>
+    <row r="43" spans="2:7">
       <c r="B43" s="152"/>
     </row>
-    <row r="44" spans="2:3">
+    <row r="44" spans="2:7">
       <c r="B44" s="152"/>
-    </row>
-    <row r="45" spans="2:3">
+      <c r="D44" s="162"/>
+    </row>
+    <row r="45" spans="2:7">
       <c r="B45" s="152"/>
     </row>
-    <row r="46" spans="2:3">
+    <row r="46" spans="2:7">
       <c r="B46" s="152"/>
     </row>
-    <row r="47" spans="2:3">
+    <row r="47" spans="2:7">
       <c r="B47" s="152"/>
     </row>
-    <row r="48" spans="2:3">
+    <row r="48" spans="2:7">
       <c r="B48" s="152"/>
     </row>
-    <row r="49" spans="2:2">
+    <row r="49" spans="1:3">
       <c r="B49" s="152"/>
     </row>
-    <row r="50" spans="2:2">
+    <row r="50" spans="1:3">
       <c r="B50" s="152"/>
     </row>
-    <row r="51" spans="2:2">
+    <row r="51" spans="1:3">
       <c r="B51" s="152"/>
     </row>
-    <row r="52" spans="2:2">
+    <row r="52" spans="1:3">
       <c r="B52" s="152"/>
     </row>
-    <row r="53" spans="2:2">
+    <row r="53" spans="1:3">
       <c r="B53" s="152"/>
     </row>
-    <row r="54" spans="2:2">
+    <row r="54" spans="1:3">
       <c r="B54" s="152"/>
     </row>
-    <row r="55" spans="2:2">
+    <row r="55" spans="1:3">
       <c r="B55" s="152"/>
     </row>
-    <row r="56" spans="2:2">
+    <row r="56" spans="1:3">
       <c r="B56" s="152"/>
     </row>
-    <row r="57" spans="2:2">
+    <row r="57" spans="1:3">
       <c r="B57" s="152"/>
     </row>
-    <row r="58" spans="2:2">
+    <row r="58" spans="1:3">
       <c r="B58" s="152"/>
     </row>
-    <row r="59" spans="2:2">
-      <c r="B59" s="152"/>
-    </row>
-    <row r="60" spans="2:2">
+    <row r="59" spans="1:3" s="151" customFormat="1">
+      <c r="A59" s="143"/>
+      <c r="B59" s="144"/>
+    </row>
+    <row r="60" spans="1:3">
       <c r="B60" s="152"/>
     </row>
-    <row r="61" spans="2:2">
+    <row r="61" spans="1:3">
       <c r="B61" s="152"/>
-    </row>
-    <row r="62" spans="2:2">
+      <c r="C61" s="145" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3">
       <c r="B62" s="152"/>
-    </row>
-    <row r="63" spans="2:2">
+      <c r="C62" s="145" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
       <c r="B63" s="152"/>
     </row>
-    <row r="64" spans="2:2">
+    <row r="64" spans="1:3">
       <c r="B64" s="152"/>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:5">
       <c r="B65" s="152"/>
     </row>
-    <row r="66" spans="2:6">
+    <row r="66" spans="2:5">
       <c r="B66" s="152"/>
-    </row>
-    <row r="67" spans="2:6">
+      <c r="C66" s="145" t="s">
+        <v>100</v>
+      </c>
+      <c r="D66" s="145">
+        <v>100</v>
+      </c>
+      <c r="E66" s="145" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5">
       <c r="B67" s="152"/>
     </row>
-    <row r="68" spans="2:6">
+    <row r="68" spans="2:5">
       <c r="B68" s="152"/>
     </row>
-    <row r="69" spans="2:6">
+    <row r="69" spans="2:5">
       <c r="B69" s="152"/>
     </row>
-    <row r="70" spans="2:6">
+    <row r="70" spans="2:5">
       <c r="B70" s="152"/>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:5">
       <c r="B71" s="152"/>
-      <c r="E71" s="145">
-        <v>0.65</v>
-      </c>
-      <c r="F71" s="145" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="72" spans="2:6">
+    </row>
+    <row r="72" spans="2:5">
       <c r="B72" s="152"/>
-      <c r="E72" s="145">
-        <f>1/E71</f>
-        <v>1.5384615384615383</v>
-      </c>
-      <c r="F72" s="145" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="73" spans="2:6">
+    </row>
+    <row r="73" spans="2:5">
       <c r="B73" s="152"/>
     </row>
-    <row r="74" spans="2:6">
+    <row r="74" spans="2:5">
       <c r="B74" s="152"/>
     </row>
-    <row r="75" spans="2:6">
+    <row r="75" spans="2:5">
       <c r="B75" s="152"/>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:5">
       <c r="B76" s="152"/>
     </row>
-    <row r="77" spans="2:6">
+    <row r="77" spans="2:5">
       <c r="B77" s="152"/>
     </row>
-    <row r="78" spans="2:6">
+    <row r="78" spans="2:5">
       <c r="B78" s="152"/>
     </row>
-    <row r="79" spans="2:6">
+    <row r="79" spans="2:5">
       <c r="B79" s="152"/>
     </row>
-    <row r="80" spans="2:6">
+    <row r="80" spans="2:5">
       <c r="B80" s="152"/>
     </row>
-    <row r="81" spans="2:7">
+    <row r="81" spans="2:2">
       <c r="B81" s="152"/>
     </row>
-    <row r="82" spans="2:7">
+    <row r="82" spans="2:2">
       <c r="B82" s="152"/>
     </row>
-    <row r="83" spans="2:7">
+    <row r="83" spans="2:2">
       <c r="B83" s="152"/>
     </row>
-    <row r="84" spans="2:7">
+    <row r="84" spans="2:2">
       <c r="B84" s="152"/>
     </row>
-    <row r="85" spans="2:7">
+    <row r="85" spans="2:2">
       <c r="B85" s="152"/>
     </row>
-    <row r="86" spans="2:7">
+    <row r="86" spans="2:2">
       <c r="B86" s="152"/>
     </row>
-    <row r="87" spans="2:7">
+    <row r="87" spans="2:2">
       <c r="B87" s="152"/>
     </row>
-    <row r="88" spans="2:7">
+    <row r="88" spans="2:2">
       <c r="B88" s="152"/>
     </row>
-    <row r="89" spans="2:7">
+    <row r="89" spans="2:2">
       <c r="B89" s="152"/>
     </row>
-    <row r="90" spans="2:7" s="151" customFormat="1">
-      <c r="B90" s="153"/>
-    </row>
-    <row r="91" spans="2:7">
+    <row r="90" spans="2:2">
+      <c r="B90" s="152"/>
+    </row>
+    <row r="91" spans="2:2">
       <c r="B91" s="152"/>
     </row>
-    <row r="92" spans="2:7">
+    <row r="92" spans="2:2">
       <c r="B92" s="152"/>
-      <c r="C92" s="145" t="s">
-        <v>105</v>
-      </c>
-      <c r="E92" s="145">
-        <v>85</v>
-      </c>
-      <c r="F92" s="145" t="s">
-        <v>76</v>
-      </c>
-      <c r="G92" s="145" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="93" spans="2:7" ht="17" thickBot="1">
+    </row>
+    <row r="93" spans="2:2">
       <c r="B93" s="152"/>
-      <c r="C93" s="145" t="s">
-        <v>110</v>
-      </c>
-      <c r="E93" s="168">
-        <v>0.01</v>
-      </c>
-      <c r="G93" s="145" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="94" spans="2:7" ht="17" thickBot="1">
+    </row>
+    <row r="94" spans="2:2">
       <c r="B94" s="152"/>
-      <c r="D94" s="185" t="s">
-        <v>138</v>
-      </c>
-      <c r="E94" s="186">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="95" spans="2:7" ht="17" thickBot="1">
+    </row>
+    <row r="95" spans="2:2">
       <c r="B95" s="152"/>
-      <c r="D95" s="185" t="s">
-        <v>139</v>
-      </c>
-      <c r="E95" s="187">
-        <f>1-(1-E94)^(1/(24*31))</f>
-        <v>5.4866766968530989E-5</v>
-      </c>
-    </row>
-    <row r="96" spans="2:7">
+    </row>
+    <row r="96" spans="2:2">
       <c r="B96" s="152"/>
-      <c r="E96" s="167"/>
-    </row>
-    <row r="97" spans="2:4">
+    </row>
+    <row r="97" spans="2:2">
       <c r="B97" s="152"/>
     </row>
-    <row r="98" spans="2:4">
+    <row r="98" spans="2:2">
       <c r="B98" s="152"/>
-      <c r="D98" s="166"/>
-    </row>
-    <row r="99" spans="2:4">
+    </row>
+    <row r="99" spans="2:2">
       <c r="B99" s="152"/>
     </row>
-    <row r="100" spans="2:4">
+    <row r="100" spans="2:2">
       <c r="B100" s="152"/>
     </row>
-    <row r="101" spans="2:4">
+    <row r="101" spans="2:2">
       <c r="B101" s="152"/>
     </row>
-    <row r="102" spans="2:4">
+    <row r="102" spans="2:2">
       <c r="B102" s="152"/>
     </row>
-    <row r="103" spans="2:4">
+    <row r="103" spans="2:2">
       <c r="B103" s="152"/>
     </row>
-    <row r="104" spans="2:4">
-      <c r="B104" s="152"/>
-    </row>
-    <row r="105" spans="2:4">
-      <c r="B105" s="152"/>
-    </row>
-    <row r="106" spans="2:4">
-      <c r="B106" s="152"/>
-    </row>
-    <row r="107" spans="2:4">
-      <c r="B107" s="152"/>
-    </row>
-    <row r="108" spans="2:4">
-      <c r="B108" s="152"/>
-    </row>
-    <row r="109" spans="2:4">
-      <c r="B109" s="152"/>
-    </row>
-    <row r="110" spans="2:4">
-      <c r="B110" s="152"/>
-    </row>
-    <row r="111" spans="2:4">
-      <c r="B111" s="152"/>
-    </row>
-    <row r="112" spans="2:4">
-      <c r="B112" s="152"/>
-    </row>
-    <row r="113" spans="1:5" s="151" customFormat="1">
-      <c r="A113" s="143"/>
-      <c r="B113" s="144"/>
-    </row>
-    <row r="114" spans="1:5">
-      <c r="B114" s="152"/>
-    </row>
-    <row r="115" spans="1:5">
-      <c r="B115" s="152"/>
-      <c r="C115" s="145" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="116" spans="1:5">
-      <c r="B116" s="152"/>
-      <c r="C116" s="145" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="117" spans="1:5">
-      <c r="B117" s="152"/>
-    </row>
-    <row r="118" spans="1:5">
-      <c r="B118" s="152"/>
-    </row>
-    <row r="119" spans="1:5">
-      <c r="B119" s="152"/>
-    </row>
-    <row r="120" spans="1:5">
-      <c r="B120" s="152"/>
-      <c r="C120" s="145" t="s">
-        <v>109</v>
-      </c>
-      <c r="D120" s="145">
-        <v>100</v>
-      </c>
-      <c r="E120" s="145" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5">
-      <c r="B121" s="152"/>
-    </row>
-    <row r="122" spans="1:5">
-      <c r="B122" s="152"/>
-    </row>
-    <row r="123" spans="1:5">
-      <c r="B123" s="152"/>
-    </row>
-    <row r="124" spans="1:5">
-      <c r="B124" s="152"/>
-    </row>
-    <row r="125" spans="1:5">
-      <c r="B125" s="152"/>
-    </row>
-    <row r="126" spans="1:5">
-      <c r="B126" s="152"/>
-    </row>
-    <row r="127" spans="1:5">
-      <c r="B127" s="152"/>
-    </row>
-    <row r="128" spans="1:5">
-      <c r="B128" s="152"/>
-    </row>
-    <row r="129" spans="2:2">
-      <c r="B129" s="152"/>
-    </row>
-    <row r="130" spans="2:2">
-      <c r="B130" s="152"/>
-    </row>
-    <row r="131" spans="2:2">
-      <c r="B131" s="152"/>
-    </row>
-    <row r="132" spans="2:2">
-      <c r="B132" s="152"/>
-    </row>
-    <row r="133" spans="2:2">
-      <c r="B133" s="152"/>
-    </row>
-    <row r="134" spans="2:2">
-      <c r="B134" s="152"/>
-    </row>
-    <row r="135" spans="2:2">
-      <c r="B135" s="152"/>
-    </row>
-    <row r="136" spans="2:2">
-      <c r="B136" s="152"/>
-    </row>
-    <row r="137" spans="2:2">
-      <c r="B137" s="152"/>
-    </row>
-    <row r="138" spans="2:2">
-      <c r="B138" s="152"/>
-    </row>
-    <row r="139" spans="2:2">
-      <c r="B139" s="152"/>
-    </row>
-    <row r="140" spans="2:2">
-      <c r="B140" s="152"/>
-    </row>
-    <row r="141" spans="2:2">
-      <c r="B141" s="152"/>
-    </row>
-    <row r="142" spans="2:2">
-      <c r="B142" s="152"/>
-    </row>
-    <row r="143" spans="2:2">
-      <c r="B143" s="152"/>
-    </row>
-    <row r="144" spans="2:2">
-      <c r="B144" s="152"/>
-    </row>
-    <row r="145" spans="2:2">
-      <c r="B145" s="152"/>
-    </row>
-    <row r="146" spans="2:2">
-      <c r="B146" s="152"/>
-    </row>
-    <row r="147" spans="2:2">
-      <c r="B147" s="152"/>
-    </row>
-    <row r="148" spans="2:2">
-      <c r="B148" s="152"/>
-    </row>
-    <row r="149" spans="2:2">
-      <c r="B149" s="152"/>
-    </row>
-    <row r="150" spans="2:2">
-      <c r="B150" s="152"/>
-    </row>
-    <row r="151" spans="2:2">
-      <c r="B151" s="152"/>
-    </row>
-    <row r="152" spans="2:2">
-      <c r="B152" s="152"/>
-    </row>
-    <row r="153" spans="2:2">
-      <c r="B153" s="152"/>
-    </row>
-    <row r="154" spans="2:2">
-      <c r="B154" s="152"/>
-    </row>
-    <row r="155" spans="2:2">
-      <c r="B155" s="152"/>
-    </row>
-    <row r="156" spans="2:2">
-      <c r="B156" s="152"/>
-    </row>
-    <row r="157" spans="2:2">
-      <c r="B157" s="152"/>
-    </row>
-    <row r="200" spans="2:6" ht="17" thickBot="1"/>
-    <row r="201" spans="2:6" s="117" customFormat="1" ht="17" thickBot="1">
-      <c r="B201" s="161"/>
-      <c r="C201" s="162" t="s">
-        <v>123</v>
-      </c>
-      <c r="D201" s="117" t="s">
-        <v>128</v>
-      </c>
-      <c r="E201" s="163">
-        <v>105088.9</v>
-      </c>
-      <c r="F201" s="117" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="202" spans="2:6" s="117" customFormat="1" ht="17" thickBot="1">
-      <c r="B202" s="161"/>
-      <c r="E202" s="117">
-        <f>E201*1000000</f>
-        <v>105088900000</v>
-      </c>
-      <c r="F202" s="117" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="203" spans="2:6" s="117" customFormat="1" ht="17" thickBot="1">
-      <c r="B203" s="161"/>
-      <c r="D203" s="117" t="s">
-        <v>130</v>
-      </c>
-      <c r="E203" s="164">
-        <f>(97.3+42.2)</f>
-        <v>139.5</v>
-      </c>
-      <c r="F203" s="117" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="204" spans="2:6" s="117" customFormat="1">
-      <c r="B204" s="161"/>
-      <c r="E204" s="117">
-        <f>E203*1000000000</f>
-        <v>139500000000</v>
-      </c>
-      <c r="F204" s="117" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="205" spans="2:6" s="117" customFormat="1">
-      <c r="B205" s="161"/>
-    </row>
-    <row r="206" spans="2:6" s="117" customFormat="1">
-      <c r="B206" s="161"/>
-      <c r="E206" s="165">
-        <f>E204/E202</f>
-        <v>1.3274475230019536</v>
-      </c>
-      <c r="F206" s="117" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="207" spans="2:6" s="117" customFormat="1">
-      <c r="B207" s="161"/>
-    </row>
-    <row r="208" spans="2:6" s="117" customFormat="1">
-      <c r="B208" s="161"/>
-    </row>
-    <row r="209" spans="2:7" s="117" customFormat="1">
-      <c r="B209" s="161"/>
-    </row>
-    <row r="210" spans="2:7" s="117" customFormat="1">
-      <c r="B210" s="161"/>
-      <c r="D210" s="117" t="str">
-        <f>Dashboard!C11</f>
-        <v>output.passenger_kms</v>
-      </c>
-      <c r="E210" s="117">
-        <f>E206*E72</f>
-        <v>2.0422269584645436</v>
-      </c>
-      <c r="F210" s="117" t="s">
-        <v>133</v>
-      </c>
-      <c r="G210" s="89" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="211" spans="2:7" s="117" customFormat="1">
-      <c r="B211" s="161"/>
-    </row>
-    <row r="212" spans="2:7" s="117" customFormat="1">
-      <c r="B212" s="161"/>
-      <c r="D212" s="117" t="str">
-        <f>Dashboard!C11</f>
-        <v>output.passenger_kms</v>
-      </c>
-      <c r="E212" s="117">
-        <f>E206*E11</f>
-        <v>1.8963536042885052</v>
-      </c>
-      <c r="G212" s="89" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="213" spans="2:7" s="117" customFormat="1">
-      <c r="B213" s="161"/>
-    </row>
-    <row r="214" spans="2:7" s="117" customFormat="1">
-      <c r="B214" s="161"/>
-    </row>
-    <row r="215" spans="2:7" s="117" customFormat="1">
-      <c r="B215" s="161"/>
-    </row>
-    <row r="216" spans="2:7" s="117" customFormat="1">
-      <c r="B216" s="161"/>
-    </row>
-    <row r="217" spans="2:7" s="117" customFormat="1">
-      <c r="B217" s="161"/>
-    </row>
-    <row r="218" spans="2:7" s="117" customFormat="1">
-      <c r="B218" s="161"/>
-    </row>
-    <row r="219" spans="2:7" s="117" customFormat="1">
-      <c r="B219" s="161"/>
-    </row>
-    <row r="220" spans="2:7" s="117" customFormat="1">
-      <c r="B220" s="161"/>
-    </row>
-    <row r="221" spans="2:7" s="117" customFormat="1">
-      <c r="B221" s="161"/>
-    </row>
-    <row r="222" spans="2:7" s="117" customFormat="1">
-      <c r="B222" s="161"/>
-    </row>
-    <row r="223" spans="2:7" s="117" customFormat="1">
-      <c r="B223" s="161"/>
-    </row>
-    <row r="224" spans="2:7" s="117" customFormat="1">
-      <c r="B224" s="161"/>
-    </row>
-    <row r="225" spans="2:2" s="117" customFormat="1">
-      <c r="B225" s="161"/>
-    </row>
-    <row r="226" spans="2:2" s="117" customFormat="1">
-      <c r="B226" s="161"/>
-    </row>
-    <row r="227" spans="2:2" s="117" customFormat="1">
-      <c r="B227" s="161"/>
-    </row>
-    <row r="228" spans="2:2" s="117" customFormat="1">
-      <c r="B228" s="161"/>
-    </row>
-    <row r="229" spans="2:2" s="117" customFormat="1">
-      <c r="B229" s="161"/>
-    </row>
-    <row r="230" spans="2:2" s="117" customFormat="1">
-      <c r="B230" s="161"/>
-    </row>
-    <row r="231" spans="2:2" s="117" customFormat="1">
-      <c r="B231" s="161"/>
-    </row>
-    <row r="232" spans="2:2" s="117" customFormat="1">
-      <c r="B232" s="161"/>
-    </row>
-    <row r="233" spans="2:2" s="117" customFormat="1">
-      <c r="B233" s="161"/>
-    </row>
-    <row r="234" spans="2:2" s="117" customFormat="1">
-      <c r="B234" s="161"/>
-    </row>
-    <row r="235" spans="2:2" s="117" customFormat="1">
-      <c r="B235" s="161"/>
-    </row>
-    <row r="236" spans="2:2" s="117" customFormat="1">
-      <c r="B236" s="161"/>
-    </row>
-    <row r="237" spans="2:2" s="117" customFormat="1">
-      <c r="B237" s="161"/>
-    </row>
-    <row r="238" spans="2:2" s="117" customFormat="1">
-      <c r="B238" s="161"/>
-    </row>
-    <row r="239" spans="2:2" s="117" customFormat="1">
-      <c r="B239" s="161"/>
-    </row>
-    <row r="240" spans="2:2" s="117" customFormat="1">
-      <c r="B240" s="161"/>
-    </row>
-    <row r="241" spans="2:2" s="117" customFormat="1">
-      <c r="B241" s="161"/>
-    </row>
-    <row r="242" spans="2:2" s="117" customFormat="1">
-      <c r="B242" s="161"/>
-    </row>
-    <row r="243" spans="2:2" s="117" customFormat="1">
-      <c r="B243" s="161"/>
-    </row>
-    <row r="244" spans="2:2" s="117" customFormat="1">
-      <c r="B244" s="161"/>
-    </row>
-    <row r="245" spans="2:2" s="117" customFormat="1">
-      <c r="B245" s="161"/>
-    </row>
-    <row r="246" spans="2:2" s="117" customFormat="1">
-      <c r="B246" s="161"/>
+    <row r="145" spans="1:7">
+      <c r="A145" s="187"/>
+      <c r="B145" s="187"/>
+      <c r="C145" s="187"/>
+      <c r="D145" s="187"/>
+      <c r="E145" s="187"/>
+      <c r="F145" s="187"/>
+      <c r="G145" s="187"/>
+    </row>
+    <row r="146" spans="1:7">
+      <c r="A146" s="187"/>
+      <c r="B146" s="187"/>
+      <c r="C146" s="187"/>
+      <c r="D146" s="187"/>
+      <c r="E146" s="187"/>
+      <c r="F146" s="187"/>
+      <c r="G146" s="187"/>
+    </row>
+    <row r="147" spans="1:7" s="117" customFormat="1">
+      <c r="A147" s="187"/>
+      <c r="B147" s="187"/>
+      <c r="C147" s="187"/>
+      <c r="D147" s="187"/>
+      <c r="E147" s="187"/>
+      <c r="F147" s="187"/>
+      <c r="G147" s="187"/>
+    </row>
+    <row r="148" spans="1:7" s="117" customFormat="1">
+      <c r="A148" s="187"/>
+      <c r="B148" s="187"/>
+      <c r="C148" s="187"/>
+      <c r="D148" s="187"/>
+      <c r="E148" s="187"/>
+      <c r="F148" s="187"/>
+      <c r="G148" s="187"/>
+    </row>
+    <row r="149" spans="1:7" s="117" customFormat="1">
+      <c r="A149" s="187"/>
+      <c r="B149" s="187"/>
+      <c r="C149" s="187"/>
+      <c r="D149" s="187"/>
+      <c r="E149" s="187"/>
+      <c r="F149" s="187"/>
+      <c r="G149" s="187"/>
+    </row>
+    <row r="150" spans="1:7" s="117" customFormat="1">
+      <c r="A150" s="187"/>
+      <c r="B150" s="187"/>
+      <c r="C150" s="187"/>
+      <c r="D150" s="187"/>
+      <c r="E150" s="187"/>
+      <c r="F150" s="187"/>
+      <c r="G150" s="187"/>
+    </row>
+    <row r="151" spans="1:7" s="117" customFormat="1">
+      <c r="A151" s="187"/>
+      <c r="B151" s="187"/>
+      <c r="C151" s="187"/>
+      <c r="D151" s="187"/>
+      <c r="E151" s="187"/>
+      <c r="F151" s="187"/>
+      <c r="G151" s="187"/>
+    </row>
+    <row r="152" spans="1:7" s="117" customFormat="1">
+      <c r="A152" s="187"/>
+      <c r="B152" s="187"/>
+      <c r="C152" s="187"/>
+      <c r="D152" s="187"/>
+      <c r="E152" s="187"/>
+      <c r="F152" s="187"/>
+      <c r="G152" s="187"/>
+    </row>
+    <row r="153" spans="1:7" s="117" customFormat="1">
+      <c r="A153" s="187"/>
+      <c r="B153" s="187"/>
+      <c r="C153" s="187"/>
+      <c r="D153" s="187"/>
+      <c r="E153" s="187"/>
+      <c r="F153" s="187"/>
+      <c r="G153" s="187"/>
+    </row>
+    <row r="154" spans="1:7" s="117" customFormat="1">
+      <c r="A154" s="187"/>
+      <c r="B154" s="187"/>
+      <c r="C154" s="187"/>
+      <c r="D154" s="187"/>
+      <c r="E154" s="187"/>
+      <c r="F154" s="187"/>
+      <c r="G154" s="187"/>
+    </row>
+    <row r="155" spans="1:7" s="117" customFormat="1">
+      <c r="A155" s="187"/>
+      <c r="B155" s="187"/>
+      <c r="C155" s="187"/>
+      <c r="D155" s="187"/>
+      <c r="E155" s="187"/>
+      <c r="F155" s="187"/>
+      <c r="G155" s="187"/>
+    </row>
+    <row r="156" spans="1:7" s="117" customFormat="1">
+      <c r="A156" s="187"/>
+      <c r="B156" s="187"/>
+      <c r="C156" s="187"/>
+      <c r="D156" s="187"/>
+      <c r="E156" s="187"/>
+      <c r="F156" s="187"/>
+      <c r="G156" s="187"/>
+    </row>
+    <row r="157" spans="1:7" s="117" customFormat="1">
+      <c r="A157" s="187"/>
+      <c r="B157" s="187"/>
+      <c r="C157" s="187"/>
+      <c r="D157" s="187"/>
+      <c r="E157" s="187"/>
+      <c r="F157" s="187"/>
+      <c r="G157" s="187"/>
+    </row>
+    <row r="158" spans="1:7" s="117" customFormat="1">
+      <c r="A158" s="187"/>
+      <c r="B158" s="187"/>
+      <c r="C158" s="187"/>
+      <c r="D158" s="187"/>
+      <c r="E158" s="187"/>
+      <c r="F158" s="187"/>
+      <c r="G158" s="187"/>
+    </row>
+    <row r="159" spans="1:7" s="117" customFormat="1">
+      <c r="A159" s="187"/>
+      <c r="B159" s="187"/>
+      <c r="C159" s="187"/>
+      <c r="D159" s="187"/>
+      <c r="E159" s="187"/>
+      <c r="F159" s="187"/>
+      <c r="G159" s="187"/>
+    </row>
+    <row r="160" spans="1:7" s="117" customFormat="1">
+      <c r="A160" s="187"/>
+      <c r="B160" s="187"/>
+      <c r="C160" s="187"/>
+      <c r="D160" s="187"/>
+      <c r="E160" s="187"/>
+      <c r="F160" s="187"/>
+      <c r="G160" s="187"/>
+    </row>
+    <row r="161" spans="1:7" s="117" customFormat="1">
+      <c r="A161" s="187"/>
+      <c r="B161" s="187"/>
+      <c r="C161" s="187"/>
+      <c r="D161" s="187"/>
+      <c r="E161" s="187"/>
+      <c r="F161" s="187"/>
+      <c r="G161" s="187"/>
+    </row>
+    <row r="162" spans="1:7" s="117" customFormat="1">
+      <c r="A162" s="187"/>
+      <c r="B162" s="187"/>
+      <c r="C162" s="187"/>
+      <c r="D162" s="187"/>
+      <c r="E162" s="187"/>
+      <c r="F162" s="187"/>
+      <c r="G162" s="187"/>
+    </row>
+    <row r="163" spans="1:7" s="117" customFormat="1">
+      <c r="A163" s="187"/>
+      <c r="B163" s="187"/>
+      <c r="C163" s="187"/>
+      <c r="D163" s="187"/>
+      <c r="E163" s="187"/>
+      <c r="F163" s="187"/>
+      <c r="G163" s="187"/>
+    </row>
+    <row r="164" spans="1:7" s="117" customFormat="1">
+      <c r="A164" s="187"/>
+      <c r="B164" s="187"/>
+      <c r="C164" s="187"/>
+      <c r="D164" s="187"/>
+      <c r="E164" s="187"/>
+      <c r="F164" s="187"/>
+      <c r="G164" s="187"/>
+    </row>
+    <row r="165" spans="1:7" s="117" customFormat="1">
+      <c r="A165" s="187"/>
+      <c r="B165" s="187"/>
+      <c r="C165" s="187"/>
+      <c r="D165" s="187"/>
+      <c r="E165" s="187"/>
+      <c r="F165" s="187"/>
+      <c r="G165" s="187"/>
+    </row>
+    <row r="166" spans="1:7" s="117" customFormat="1">
+      <c r="A166" s="187"/>
+      <c r="B166" s="187"/>
+      <c r="C166" s="187"/>
+      <c r="D166" s="187"/>
+      <c r="E166" s="187"/>
+      <c r="F166" s="187"/>
+      <c r="G166" s="187"/>
+    </row>
+    <row r="167" spans="1:7" s="117" customFormat="1">
+      <c r="A167" s="187"/>
+      <c r="B167" s="187"/>
+      <c r="C167" s="187"/>
+      <c r="D167" s="187"/>
+      <c r="E167" s="187"/>
+      <c r="F167" s="187"/>
+      <c r="G167" s="187"/>
+    </row>
+    <row r="168" spans="1:7" s="117" customFormat="1">
+      <c r="A168" s="187"/>
+      <c r="B168" s="187"/>
+      <c r="C168" s="187"/>
+      <c r="D168" s="187"/>
+      <c r="E168" s="187"/>
+      <c r="F168" s="187"/>
+      <c r="G168" s="187"/>
+    </row>
+    <row r="169" spans="1:7" s="117" customFormat="1">
+      <c r="A169" s="187"/>
+      <c r="B169" s="187"/>
+      <c r="C169" s="187"/>
+      <c r="D169" s="187"/>
+      <c r="E169" s="187"/>
+      <c r="F169" s="187"/>
+      <c r="G169" s="187"/>
+    </row>
+    <row r="170" spans="1:7" s="117" customFormat="1">
+      <c r="A170" s="187"/>
+      <c r="B170" s="187"/>
+      <c r="C170" s="187"/>
+      <c r="D170" s="187"/>
+      <c r="E170" s="187"/>
+      <c r="F170" s="187"/>
+      <c r="G170" s="187"/>
+    </row>
+    <row r="171" spans="1:7" s="117" customFormat="1">
+      <c r="A171" s="187"/>
+      <c r="B171" s="187"/>
+      <c r="C171" s="187"/>
+      <c r="D171" s="187"/>
+      <c r="E171" s="187"/>
+      <c r="F171" s="187"/>
+      <c r="G171" s="187"/>
+    </row>
+    <row r="172" spans="1:7" s="117" customFormat="1">
+      <c r="A172" s="187"/>
+      <c r="B172" s="187"/>
+      <c r="C172" s="187"/>
+      <c r="D172" s="187"/>
+      <c r="E172" s="187"/>
+      <c r="F172" s="187"/>
+      <c r="G172" s="187"/>
+    </row>
+    <row r="173" spans="1:7" s="117" customFormat="1">
+      <c r="A173" s="187"/>
+      <c r="B173" s="187"/>
+      <c r="C173" s="187"/>
+      <c r="D173" s="187"/>
+      <c r="E173" s="187"/>
+      <c r="F173" s="187"/>
+      <c r="G173" s="187"/>
+    </row>
+    <row r="174" spans="1:7" s="117" customFormat="1">
+      <c r="A174" s="187"/>
+      <c r="B174" s="187"/>
+      <c r="C174" s="187"/>
+      <c r="D174" s="187"/>
+      <c r="E174" s="187"/>
+      <c r="F174" s="187"/>
+      <c r="G174" s="187"/>
+    </row>
+    <row r="175" spans="1:7" s="117" customFormat="1">
+      <c r="A175" s="187"/>
+      <c r="B175" s="187"/>
+      <c r="C175" s="187"/>
+      <c r="D175" s="187"/>
+      <c r="E175" s="187"/>
+      <c r="F175" s="187"/>
+      <c r="G175" s="187"/>
+    </row>
+    <row r="176" spans="1:7" s="117" customFormat="1">
+      <c r="A176" s="187"/>
+      <c r="B176" s="187"/>
+      <c r="C176" s="187"/>
+      <c r="D176" s="187"/>
+      <c r="E176" s="187"/>
+      <c r="F176" s="187"/>
+      <c r="G176" s="187"/>
+    </row>
+    <row r="177" spans="1:7" s="117" customFormat="1">
+      <c r="A177" s="187"/>
+      <c r="B177" s="187"/>
+      <c r="C177" s="187"/>
+      <c r="D177" s="187"/>
+      <c r="E177" s="187"/>
+      <c r="F177" s="187"/>
+      <c r="G177" s="187"/>
+    </row>
+    <row r="178" spans="1:7" s="117" customFormat="1">
+      <c r="A178" s="187"/>
+      <c r="B178" s="187"/>
+      <c r="C178" s="187"/>
+      <c r="D178" s="187"/>
+      <c r="E178" s="187"/>
+      <c r="F178" s="187"/>
+      <c r="G178" s="187"/>
+    </row>
+    <row r="179" spans="1:7" s="117" customFormat="1">
+      <c r="A179" s="187"/>
+      <c r="B179" s="187"/>
+      <c r="C179" s="187"/>
+      <c r="D179" s="187"/>
+      <c r="E179" s="187"/>
+      <c r="F179" s="187"/>
+      <c r="G179" s="187"/>
+    </row>
+    <row r="180" spans="1:7" s="117" customFormat="1">
+      <c r="A180" s="187"/>
+      <c r="B180" s="187"/>
+      <c r="C180" s="187"/>
+      <c r="D180" s="187"/>
+      <c r="E180" s="187"/>
+      <c r="F180" s="187"/>
+      <c r="G180" s="187"/>
+    </row>
+    <row r="181" spans="1:7" s="117" customFormat="1">
+      <c r="A181" s="187"/>
+      <c r="B181" s="187"/>
+      <c r="C181" s="187"/>
+      <c r="D181" s="187"/>
+      <c r="E181" s="187"/>
+      <c r="F181" s="187"/>
+      <c r="G181" s="187"/>
+    </row>
+    <row r="182" spans="1:7" s="117" customFormat="1">
+      <c r="A182" s="187"/>
+      <c r="B182" s="187"/>
+      <c r="C182" s="187"/>
+      <c r="D182" s="187"/>
+      <c r="E182" s="187"/>
+      <c r="F182" s="187"/>
+      <c r="G182" s="187"/>
+    </row>
+    <row r="183" spans="1:7" s="117" customFormat="1">
+      <c r="A183" s="187"/>
+      <c r="B183" s="187"/>
+      <c r="C183" s="187"/>
+      <c r="D183" s="187"/>
+      <c r="E183" s="187"/>
+      <c r="F183" s="187"/>
+      <c r="G183" s="187"/>
+    </row>
+    <row r="184" spans="1:7" s="117" customFormat="1">
+      <c r="A184" s="187"/>
+      <c r="B184" s="187"/>
+      <c r="C184" s="187"/>
+      <c r="D184" s="187"/>
+      <c r="E184" s="187"/>
+      <c r="F184" s="187"/>
+      <c r="G184" s="187"/>
+    </row>
+    <row r="185" spans="1:7" s="117" customFormat="1">
+      <c r="A185" s="187"/>
+      <c r="B185" s="187"/>
+      <c r="C185" s="187"/>
+      <c r="D185" s="187"/>
+      <c r="E185" s="187"/>
+      <c r="F185" s="187"/>
+      <c r="G185" s="187"/>
+    </row>
+    <row r="186" spans="1:7" s="117" customFormat="1">
+      <c r="A186" s="187"/>
+      <c r="B186" s="187"/>
+      <c r="C186" s="187"/>
+      <c r="D186" s="187"/>
+      <c r="E186" s="187"/>
+      <c r="F186" s="187"/>
+      <c r="G186" s="187"/>
+    </row>
+    <row r="187" spans="1:7" s="117" customFormat="1">
+      <c r="A187" s="187"/>
+      <c r="B187" s="187"/>
+      <c r="C187" s="187"/>
+      <c r="D187" s="187"/>
+      <c r="E187" s="187"/>
+      <c r="F187" s="187"/>
+      <c r="G187" s="187"/>
+    </row>
+    <row r="188" spans="1:7" s="117" customFormat="1">
+      <c r="A188" s="187"/>
+      <c r="B188" s="187"/>
+      <c r="C188" s="187"/>
+      <c r="D188" s="187"/>
+      <c r="E188" s="187"/>
+      <c r="F188" s="187"/>
+      <c r="G188" s="187"/>
+    </row>
+    <row r="189" spans="1:7" s="117" customFormat="1">
+      <c r="A189" s="187"/>
+      <c r="B189" s="187"/>
+      <c r="C189" s="187"/>
+      <c r="D189" s="187"/>
+      <c r="E189" s="187"/>
+      <c r="F189" s="187"/>
+      <c r="G189" s="187"/>
+    </row>
+    <row r="190" spans="1:7" s="117" customFormat="1">
+      <c r="A190" s="187"/>
+      <c r="B190" s="187"/>
+      <c r="C190" s="187"/>
+      <c r="D190" s="187"/>
+      <c r="E190" s="187"/>
+      <c r="F190" s="187"/>
+      <c r="G190" s="187"/>
+    </row>
+    <row r="191" spans="1:7" s="117" customFormat="1">
+      <c r="A191" s="187"/>
+      <c r="B191" s="187"/>
+      <c r="C191" s="187"/>
+      <c r="D191" s="187"/>
+      <c r="E191" s="187"/>
+      <c r="F191" s="187"/>
+      <c r="G191" s="187"/>
+    </row>
+    <row r="192" spans="1:7" s="117" customFormat="1">
+      <c r="A192" s="187"/>
+      <c r="B192" s="187"/>
+      <c r="C192" s="187"/>
+      <c r="D192" s="187"/>
+      <c r="E192" s="187"/>
+      <c r="F192" s="187"/>
+      <c r="G192" s="187"/>
+    </row>
+    <row r="193" spans="1:7">
+      <c r="A193" s="187"/>
+      <c r="B193" s="187"/>
+      <c r="C193" s="187"/>
+      <c r="D193" s="187"/>
+      <c r="E193" s="187"/>
+      <c r="F193" s="187"/>
+      <c r="G193" s="187"/>
+    </row>
+    <row r="194" spans="1:7">
+      <c r="A194" s="187"/>
+      <c r="B194" s="187"/>
+      <c r="C194" s="187"/>
+      <c r="D194" s="187"/>
+      <c r="E194" s="187"/>
+      <c r="F194" s="187"/>
+      <c r="G194" s="187"/>
+    </row>
+    <row r="195" spans="1:7">
+      <c r="A195" s="187"/>
+      <c r="B195" s="187"/>
+      <c r="C195" s="187"/>
+      <c r="D195" s="187"/>
+      <c r="E195" s="187"/>
+      <c r="F195" s="187"/>
+      <c r="G195" s="187"/>
+    </row>
+    <row r="196" spans="1:7">
+      <c r="A196" s="187"/>
+      <c r="B196" s="187"/>
+      <c r="C196" s="187"/>
+      <c r="D196" s="187"/>
+      <c r="E196" s="187"/>
+      <c r="F196" s="187"/>
+      <c r="G196" s="187"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
